--- a/docs/G11_UAT.xlsx
+++ b/docs/G11_UAT.xlsx
@@ -8,6 +8,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UAT" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="desc" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ผู้ทดสอบและการลงนาม" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="181029" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -44,8 +45,15 @@
       <color rgb="FF212529"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -56,6 +64,16 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
   </fills>
@@ -86,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -108,6 +126,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -519,8 +549,8 @@
     <col width="46" customWidth="1" style="8" min="7" max="7"/>
     <col width="46" customWidth="1" style="8" min="8" max="8"/>
     <col width="46" customWidth="1" style="8" min="9" max="9"/>
-    <col width="26" customWidth="1" style="8" min="10" max="10"/>
-    <col width="14" customWidth="1" style="8" min="11" max="11"/>
+    <col width="52" customWidth="1" style="8" min="10" max="10"/>
+    <col width="18" customWidth="1" style="8" min="11" max="11"/>
     <col width="34" customWidth="1" style="8" min="12" max="12"/>
     <col width="10.83203125" customWidth="1" style="2" min="13" max="16384"/>
   </cols>
@@ -587,7 +617,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="96" customHeight="1">
+    <row r="2" ht="170" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
           <t>SIT-001</t>
@@ -636,15 +666,23 @@
           <t>สมัครเสร็จแล้วเข้าใช้งานได้ทันที และถ้ากรอกผิดจะมีข้อความภาษาไทยบอกว่าผิดตรงไหน</t>
         </is>
       </c>
-      <c r="J2" s="6" t="n"/>
-      <c r="K2" s="6" t="n"/>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>ทดสอบบนมือถือจริง 10/09/2569 01:40 น. สมัครบัญชีลูกค้าใหม่ด้วยอีเมล patcharin.taraboon@gmail.com และเบอร์ 0622934006 สมัครจนจบได้เองโดยไม่ต้องมีคนแนะนำ เข้าใช้งานได้ทันทีหลังสมัคร และหน้าโปรไฟล์แสดงป้าย "บัญชีลูกค้า" พร้อมชื่อและเบอร์ที่กรอกไว้ถูกต้องครบทุกช่อง</t>
+        </is>
+      </c>
+      <c r="K2" s="12" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
-          <t>ผู้ทดสอบ: ลูกค้า | สังเกตว่าผู้ใช้สับสนตรงขั้นตอนไหนบ้าง</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="96" customHeight="1">
+          <t>ผู้ทดสอบ: เจ้าของโครงงาน (บทบาทลูกค้า) | มีภาพหน้าจอประกอบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="170" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>SIT-005</t>
@@ -692,15 +730,23 @@
           <t>เข้าสู่ระบบได้และเป็นบัญชีเดิม โดยผู้ใช้ไม่ต้องเลือกเองว่ากรอกอะไรลงไป</t>
         </is>
       </c>
-      <c r="J3" s="6" t="n"/>
-      <c r="K3" s="6" t="n"/>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>ทดสอบบนมือถือจริง 10/09/2569 01:42 น. ออกจากระบบแล้วเข้าใหม่โดยกรอกเบอร์ 0622934006 ในช่องแรกแทนอีเมล เข้าสู่ระบบได้และเป็นบัญชีเดิม ผู้ใช้ไม่ต้องเลือกเองว่ากรอกอะไรลงไป ระบบแยกประเภทให้เอง</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>ผู้ทดสอบ: ลูกค้า | ถามผู้ใช้ว่ารู้ไหมว่าช่องนี้กรอกได้ทั้งสองอย่าง</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="96" customHeight="1">
+          <t>ผู้ทดสอบ: เจ้าของโครงงาน (บทบาทลูกค้า) | มีภาพหน้าจอประกอบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="170" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>SIT-007</t>
@@ -749,15 +795,23 @@
           <t>ตั้งรหัสผ่านใหม่สำเร็จและเข้าสู่ระบบได้ รหัสเดิมใช้ไม่ได้อีก</t>
         </is>
       </c>
-      <c r="J4" s="6" t="n"/>
-      <c r="K4" s="6" t="n"/>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>ทดสอบจริง 10/09/2569 01:43 น. ขอตั้งรหัสผ่านใหม่ ระบบออกรหัส 6 หลักและลิงก์ให้พร้อมกัน ตั้งรหัสใหม่สำเร็จและกลับเข้าสู่ระบบด้วยรหัสใหม่ได้ ข้อสังเกต : เซิร์ฟเวอร์ยังไม่ได้ตั้งค่า SMTP อีเมลจึงไม่ถูกส่งออกจริง ระบบรองรับกรณีนี้ไว้แล้วโดยแสดงกล่อง "โหมดสาธิต" พร้อมกรอกรหัส 6 หลักให้อัตโนมัติในแอป ผู้ทดสอบเลือกใช้เส้นทางลิงก์ผ่านเบราว์เซอร์แทน จึงต้องเปิดดูรหัสจาก Log ของ Render</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>ผู้ทดสอบ: ลูกค้า | จับเวลาว่าตั้งแต่กดจนเข้าได้ใช้เวลากี่นาที</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="96" customHeight="1">
+          <t>ผู้ทดสอบ: เจ้าของโครงงาน (บทบาทลูกค้า) | มีภาพหน้าจอประกอบ | *** ก่อนใช้งานจริงต้องตั้งค่า SMTP บน Render ไม่งั้นผู้ใช้จริงจะไม่ได้รับอีเมล ***</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="170" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>SIT-028</t>
@@ -805,15 +859,23 @@
           <t>ผลลัพธ์ตรงกับสิ่งที่กรอง และเรียงลำดับถูกต้องตามที่เลือก</t>
         </is>
       </c>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="6" t="n"/>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>รอทดสอบ — จุดที่ต้องดู : ผลค้นหาตรงกับคำที่พิมพ์หรือไม่ · กรองหมวดหมู่และช่วงราคาแล้วผลลัพธ์เปลี่ยนถูกต้องหรือไม่ · เรียงราคาน้อยไปมากแล้วเรียงถูกจริงหรือไม่ · ผู้ใช้บอกว่าตัวกรองขาดอะไร</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>รอทดสอบ</t>
+        </is>
+      </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
           <t>ผู้ทดสอบ: ลูกค้า | ถามว่าตัวกรองที่มีเพียงพอไหม ขาดอะไร</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="96" customHeight="1">
+    <row r="6" ht="170" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>SIT-026</t>
@@ -862,15 +924,23 @@
           <t>เห็นร้านใกล้ตัวพร้อมระยะทางเป็นกิโลเมตร และเมื่อไม่ให้สิทธิ์ตำแหน่งก็ยังดูรายการร้านได้</t>
         </is>
       </c>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>รอทดสอบ — จุดที่ต้องดู : เห็นหมุดร้านพร้อมระยะทางเป็นกิโลเมตรหรือไม่ · เปลี่ยนรัศมีเป็น 1 กม. แล้วร้านลดลงหรือไม่ · ปฏิเสธสิทธิ์ตำแหน่งแล้วยังดูรายการร้านได้หรือไม่ · ระยะทางที่แสดงใกล้เคียงความจริงหรือไม่</t>
+        </is>
+      </c>
+      <c r="K6" s="11" t="inlineStr">
+        <is>
+          <t>รอทดสอบ</t>
+        </is>
+      </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
           <t>ผู้ทดสอบ: ลูกค้า | ตรวจว่าระยะทางที่แสดงใกล้เคียงความจริง</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="96" customHeight="1">
+    <row r="7" ht="170" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>SIT-014</t>
@@ -919,15 +989,23 @@
           <t>จองสำเร็จ เห็น QR Code กับรหัส 4 หลัก และเปิดดูซ้ำได้ตลอดเวลาที่คิวยังไม่หมดอายุ</t>
         </is>
       </c>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>[ตรวจระดับ API 10/09/2569 01:03] จองสำเร็จ ได้ reservation_id 4 และรหัสรับ 1898 จำนวนคงเหลือของโพสต์ลดจาก 3 เหลือ 2 ทันที และ expires_at ถูกตั้งเป็น 01:15:15 ตรงตาม hold_minutes 12 นาทีที่ร้านกำหนด — ยังไม่ได้ตรวจการแสดง QR บนหน้าจอ  ยังต้องดูบนหน้าจอ : QR Code แสดงผลถูกต้อง และเปิดดูซ้ำได้หลังปิด-เปิดแอป</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>รอยืนยันบนแอป</t>
+        </is>
+      </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>ผู้ทดสอบ: ลูกค้า | ถามว่าเข้าใจไหมว่าต้องทำอะไรต่อ</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="96" customHeight="1">
+          <t>ผู้ทดสอบ: ลูกค้า | ถามว่าเข้าใจไหมว่าต้องทำอะไรต่อ  ||  ตรวจด้วยสคริปต์ยิง API จริงเข้า https://saveeats.onrender.com ด้วยบัญชี seed (customer1@test.com / seller1@test.com) ยังไม่ใช่การทดสอบโดยผู้ใช้บนหน้าจอ ต้องเปิดแอปยืนยันด้วยตาแล้วจึงกรอกช่อง Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="170" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>SIT-017</t>
@@ -976,15 +1054,23 @@
           <t>เห็นเวลานับถอยหลังชัดเจน และได้รับข้อความเตือนก่อนหมดเวลา 1 ครั้ง ไม่ถูกเตือนซ้ำ ๆ</t>
         </is>
       </c>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>[ตรวจระดับ API 10/09/2569 01:03-01:22] จองเวลา 01:03:52 คิวหมดอายุ 01:15:52 ระบบส่งข้อความ "ใกล้หมดเวลารับอาหาร — เหลืออีกประมาณ 10 นาที" เมื่อ 01:05:41 งานเบื้องหลังวิ่งอีก 3 รอบหลังจากนั้น (01:10 / 01:15 / 01:20) ยังคงมีข้อความเตือนเพียง 1 ฉบับ ไม่มีการเตือนซ้ำ — ยังไม่ได้ตรวจตัวนับถอยหลังบนหน้าจอ  ยังต้องดูบนหน้าจอ : ตัวนับถอยหลังเดินถูกต้อง และข้อความเตือนโผล่ในหน้าการแจ้งเตือนของลูกค้า</t>
+        </is>
+      </c>
+      <c r="K8" s="11" t="inlineStr">
+        <is>
+          <t>รอยืนยันบนแอป</t>
+        </is>
+      </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>ผู้ทดสอบ: ลูกค้า | ข้อนี้ครอบคลุม RQ-045 ที่เพิ่งพัฒนาเสร็จ</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="96" customHeight="1">
+          <t>ผู้ทดสอบ: ลูกค้า | ข้อนี้ครอบคลุม RQ-045 ที่เพิ่งพัฒนาเสร็จ  ||  ตรวจด้วยสคริปต์ยิง API จริงเข้า https://saveeats.onrender.com ด้วยบัญชี seed (customer1@test.com / seller1@test.com) ยังไม่ใช่การทดสอบโดยผู้ใช้บนหน้าจอ ต้องเปิดแอปยืนยันด้วยตาแล้วจึงกรอกช่อง Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="170" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>SIT-018</t>
@@ -1032,15 +1118,23 @@
           <t>ยกเลิกสำเร็จ และจำนวนคงเหลือของรายการนั้นเพิ่มกลับมาให้คนอื่นจองต่อได้</t>
         </is>
       </c>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>[ตรวจระดับ API 10/09/2569 01:03] ลูกค้ายกเลิกเอง สถานะเปลี่ยนเป็น cancelled และจำนวนคงเหลือของโพสต์กลับจาก 2 เป็น 3 ทันทีในคำขอเดียวกัน  ยังต้องดูบนหน้าจอ : ข้อความเตือนก่อนกดยกเลิกอ่านแล้วเข้าใจ และรายการหายจากหน้าการจอง</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>รอยืนยันบนแอป</t>
+        </is>
+      </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>ผู้ทดสอบ: ลูกค้า | สังเกตว่าข้อความเตือนก่อนยกเลิกชัดพอไหม</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="96" customHeight="1">
+          <t>ผู้ทดสอบ: ลูกค้า | สังเกตว่าข้อความเตือนก่อนยกเลิกชัดพอไหม  ||  ตรวจด้วยสคริปต์ยิง API จริงเข้า https://saveeats.onrender.com ด้วยบัญชี seed (customer1@test.com / seller1@test.com) ยังไม่ใช่การทดสอบโดยผู้ใช้บนหน้าจอ ต้องเปิดแอปยืนยันด้วยตาแล้วจึงกรอกช่อง Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="170" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>SIT-046</t>
@@ -1088,15 +1182,23 @@
           <t>รีวิวถูกบันทึก คะแนนเฉลี่ยของร้านเปลี่ยนตาม และรีวิวการจองเดิมซ้ำอีกครั้งไม่ได้</t>
         </is>
       </c>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>รอทดสอบ — จุดที่ต้องดู : เขียนรีวิวได้เฉพาะการจองที่รับอาหารแล้วหรือไม่ · คะแนนเฉลี่ยของร้านเปลี่ยนตามทันทีหรือไม่ · รีวิวการจองเดิมซ้ำแล้วระบบปฏิเสธหรือไม่ · คะแนนที่เห็นตรงกันทุกหน้าจอหรือไม่</t>
+        </is>
+      </c>
+      <c r="K10" s="11" t="inlineStr">
+        <is>
+          <t>รอทดสอบ</t>
+        </is>
+      </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
           <t>ผู้ทดสอบ: ลูกค้า | ตรวจว่าคะแนนที่เห็นตรงกันทุกหน้าจอ</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="96" customHeight="1">
+    <row r="11" ht="170" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>SIT-008</t>
@@ -1144,15 +1246,23 @@
           <t>ลงทะเบียนสำเร็จ ร้านขึ้นสถานะรออนุมัติ พร้อมข้อความอธิบายว่ายังลงขายไม่ได้และต้องรออะไร</t>
         </is>
       </c>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>รอทดสอบ — จุดที่ต้องดู : ลงทะเบียนร้านจนจบได้หรือไม่ · ปักหมุดตำแหน่งได้หรือไม่ · หน้าแรกขึ้นสถานะรออนุมัติพร้อมคำอธิบายหรือไม่ · เจ้าของร้านเข้าใจไหมว่าทำไมยังขายไม่ได้</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>รอทดสอบ</t>
+        </is>
+      </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
           <t>ผู้ทดสอบ: เจ้าของร้าน | ถามว่าเข้าใจไหมว่าทำไมยังขายไม่ได้</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="96" customHeight="1">
+    <row r="12" ht="170" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>SIT-011</t>
@@ -1201,15 +1311,23 @@
           <t>โพสต์ขึ้นให้ลูกค้าเห็น ระบบคิดเปอร์เซ็นต์ส่วนลดให้เอง และข้อมูลตรงกับที่ร้านกรอกทุกช่อง</t>
         </is>
       </c>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>รอทดสอบ — จุดที่ต้องดู : เพิ่มเมนูแล้วลงขายได้หรือไม่ · ระบบคิดเปอร์เซ็นต์ส่วนลดให้เองถูกต้องหรือไม่ · แนบรูปแล้วรูปขึ้นฝั่งลูกค้าหรือไม่ · ข้อมูลตรงกับที่ร้านกรอกครบทุกช่องหรือไม่ · ใช้เวลากี่นาทีตั้งแต่เริ่มจนโพสต์ขึ้น</t>
+        </is>
+      </c>
+      <c r="K12" s="11" t="inlineStr">
+        <is>
+          <t>รอทดสอบ</t>
+        </is>
+      </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
           <t>ผู้ทดสอบ: เจ้าของร้าน | จับเวลาตั้งแต่เริ่มจนโพสต์ขึ้น</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="96" customHeight="1">
+    <row r="13" ht="170" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>SIT-036</t>
@@ -1257,15 +1375,23 @@
           <t>มีจุดแดงขึ้นบนกระดิ่ง และในหน้าการแจ้งเตือนมีข้อความว่ามีการจองใหม่ พร้อมชื่ออาหาร</t>
         </is>
       </c>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>[ตรวจระดับ API 10/09/2569 01:03:16] ร้านได้รับข้อความ "มีการจองใหม่ — มีลูกค้าจอง ข้าวกะเพราหมูสับไข่ดาว จากร้านของคุณ" ภายในไม่กี่วินาทีหลังลูกค้ากดจอง — ยังไม่ได้ตรวจจุดแดงบนกระดิ่งในแอป  ยังต้องดูบนหน้าจอ : จุดแดงขึ้นบนกระดิ่งที่หน้าแรกของร้าน และกดเข้าไปอ่านข้อความได้</t>
+        </is>
+      </c>
+      <c r="K13" s="11" t="inlineStr">
+        <is>
+          <t>รอยืนยันบนแอป</t>
+        </is>
+      </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>ผู้ทดสอบ: เจ้าของร้าน | ถามว่าเห็นจุดแดงเร็วพอที่จะเตรียมของทันไหม</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="96" customHeight="1">
+          <t>ผู้ทดสอบ: เจ้าของร้าน | ถามว่าเห็นจุดแดงเร็วพอที่จะเตรียมของทันไหม  ||  ตรวจด้วยสคริปต์ยิง API จริงเข้า https://saveeats.onrender.com ด้วยบัญชี seed (customer1@test.com / seller1@test.com) ยังไม่ใช่การทดสอบโดยผู้ใช้บนหน้าจอ ต้องเปิดแอปยืนยันด้วยตาแล้วจึงกรอกช่อง Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="170" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
           <t>SIT-018</t>
@@ -1314,15 +1440,23 @@
           <t>ร้านได้รับข้อความว่าลูกค้ายกเลิกการจอง และจำนวนคงเหลือกลับมาให้ขายต่อได้</t>
         </is>
       </c>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>[ตรวจระดับ API 10/09/2569 01:03:32] ลูกค้ากดยกเลิก ร้านได้รับข้อความ "ลูกค้ายกเลิกการจอง — ลูกค้ายกเลิกการจอง ข้าวกะเพราหมูสับไข่ดาว ของถูกคืนเข้าระบบให้ขายต่อแล้ว" และจำนวนคงเหลือกลับมาเป็น 3 — ยังไม่ได้ตรวจการเปิดอ่านผ่านกระดิ่งในแอป  ยังต้องดูบนหน้าจอ : ร้านกดกระดิ่งแล้วเห็นข้อความ "ลูกค้ายกเลิกการจอง"</t>
+        </is>
+      </c>
+      <c r="K14" s="11" t="inlineStr">
+        <is>
+          <t>รอยืนยันบนแอป</t>
+        </is>
+      </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
-          <t>ผู้ทดสอบ: เจ้าของร้าน | ข้อนี้คือครึ่งหลังของ RQ-046 ที่เพิ่งพัฒนาเสร็จ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="96" customHeight="1">
+          <t>ผู้ทดสอบ: เจ้าของร้าน | ข้อนี้คือครึ่งหลังของ RQ-046 ที่เพิ่งพัฒนาเสร็จ  ||  ตรวจด้วยสคริปต์ยิง API จริงเข้า https://saveeats.onrender.com ด้วยบัญชี seed (customer1@test.com / seller1@test.com) ยังไม่ใช่การทดสอบโดยผู้ใช้บนหน้าจอ ต้องเปิดแอปยืนยันด้วยตาแล้วจึงกรอกช่อง Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="170" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>SIT-021</t>
@@ -1371,15 +1505,23 @@
           <t>ยืนยันสำเร็จภายในไม่กี่วินาที และสถานะเปลี่ยนเป็นรับอาหารแล้วตรงกันทั้งสองฝั่ง</t>
         </is>
       </c>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>รอทดสอบ — จุดที่ต้องดู : สแกน QR แล้วสถานะเปลี่ยนภายในกี่วินาที · สแกนไม่ได้แล้วกรอกรหัส 4 หลักแทนได้หรือไม่ · สถานะเปลี่ยนตรงกันทั้งฝั่งร้านและฝั่งลูกค้าหรือไม่ · ทดสอบในที่แสงน้อยแล้วยังสแกนติดหรือไม่</t>
+        </is>
+      </c>
+      <c r="K15" s="11" t="inlineStr">
+        <is>
+          <t>รอทดสอบ</t>
+        </is>
+      </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
           <t>ผู้ทดสอบ: เจ้าของร้าน | ทดสอบในที่แสงน้อยด้วย เพราะหน้าร้านจริงตอนเย็นมืด</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="96" customHeight="1">
+    <row r="16" ht="170" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
           <t>SIT-022</t>
@@ -1427,15 +1569,23 @@
           <t>ทั้ง 3 กรณีถูกปฏิเสธ และขึ้นข้อความภาษาไทยที่บอกชัดว่าเป็นเพราะอะไร ไม่ใช่ข้อความรวม ๆ</t>
         </is>
       </c>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>รอทดสอบ — จุดที่ต้องดู : สแกน QR ที่ใช้ไปแล้วถูกปฏิเสธหรือไม่ · ร้านอื่นสแกน QR ใบเดียวกันถูกปฏิเสธหรือไม่ · สแกนคิวที่หมดเวลาถูกปฏิเสธหรือไม่ · ข้อความที่ขึ้นบอกเหตุผลต่างกันทั้ง 3 กรณีหรือไม่ · อ่านแล้วรู้ไหมว่าต้องทำอะไรต่อ</t>
+        </is>
+      </c>
+      <c r="K16" s="11" t="inlineStr">
+        <is>
+          <t>รอทดสอบ</t>
+        </is>
+      </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
           <t>ผู้ทดสอบ: เจ้าของร้าน | ถามว่าอ่านข้อความแล้วรู้ไหมว่าต้องทำอะไรต่อ</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="96" customHeight="1">
+    <row r="17" ht="170" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>SIT-037</t>
@@ -1483,15 +1633,23 @@
           <t>คิวถูกปิดเป็นหมดเวลาเอง และจำนวนคงเหลือกลับมาเท่าเดิมโดยไม่เกินจำนวนจริง</t>
         </is>
       </c>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>[ตรวจระดับ API 10/09/2569 01:20:41] ปล่อยคิวจนเลยเวลา 01:15:52 งานเบื้องหลังรอบ 01:20:41 ปิดคิวเป็น expired เอง จำนวนคงเหลือกลับเป็น 3 เท่าเดิมไม่เกินจริง และลูกค้าได้รับข้อความ "การจองหมดอายุ"  ยังต้องดูบนหน้าจอ : จำนวนคงเหลือในหน้าโพสต์ของร้านกลับมาเท่าเดิม</t>
+        </is>
+      </c>
+      <c r="K17" s="11" t="inlineStr">
+        <is>
+          <t>รอยืนยันบนแอป</t>
+        </is>
+      </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>ผู้ทดสอบ: เจ้าของร้าน | ตรวจว่าจำนวนไม่งอกเกินของที่มีอยู่จริง</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="96" customHeight="1">
+          <t>ผู้ทดสอบ: เจ้าของร้าน | ตรวจว่าจำนวนไม่งอกเกินของที่มีอยู่จริง  ||  ตรวจด้วยสคริปต์ยิง API จริงเข้า https://saveeats.onrender.com ด้วยบัญชี seed (customer1@test.com / seller1@test.com) ยังไม่ใช่การทดสอบโดยผู้ใช้บนหน้าจอ ต้องเปิดแอปยืนยันด้วยตาแล้วจึงกรอกช่อง Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="170" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
           <t>SIT-059</t>
@@ -1539,15 +1697,23 @@
           <t>เห็นรายการครบ กรองได้ถูกต้อง และข้อมูลตรงกับที่ลูกค้าเห็นในเครื่องของตัวเอง</t>
         </is>
       </c>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>รอทดสอบ — จุดที่ต้องดู : เห็นรายการจองครบหรือไม่ · กรองเฉพาะรอมารับได้หรือไม่ · ข้อมูลตรงกับที่ลูกค้าเห็นในเครื่องตัวเองหรือไม่ · ข้อมูลที่แสดงพอใช้เตรียมของไหม</t>
+        </is>
+      </c>
+      <c r="K18" s="11" t="inlineStr">
+        <is>
+          <t>รอทดสอบ</t>
+        </is>
+      </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
           <t>ผู้ทดสอบ: เจ้าของร้าน | ถามว่าข้อมูลที่แสดงพอใช้เตรียมของไหม</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="96" customHeight="1">
+    <row r="19" ht="170" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t>SIT-029</t>
@@ -1596,15 +1762,23 @@
           <t>ร้านที่อนุมัติปรากฏให้ลูกค้าเห็นทันที ร้านที่ไม่อนุมัติไม่ปรากฏ และเห็นเหตุผลที่ผู้ดูแลเขียน</t>
         </is>
       </c>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>รอทดสอบ — จุดที่ต้องดู : อนุมัติแล้วร้านขึ้นให้ลูกค้าเห็นทันทีหรือไม่ · ไม่อนุมัติแล้วร้านไม่ปรากฏหรือไม่ · ร้านที่ถูกปฏิเสธเห็นเหตุผลที่ผู้ดูแลเขียนหรือไม่ · เหตุผลที่ส่งกลับอ่านแล้วแก้ไขต่อได้หรือไม่</t>
+        </is>
+      </c>
+      <c r="K19" s="11" t="inlineStr">
+        <is>
+          <t>รอทดสอบ</t>
+        </is>
+      </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
           <t>ผู้ทดสอบ: ผู้ดูแลระบบ | ตรวจว่าเหตุผลที่ส่งกลับอ่านแล้วแก้ไขต่อได้</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="96" customHeight="1">
+    <row r="20" ht="170" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
           <t>SIT-032</t>
@@ -1653,15 +1827,23 @@
           <t>ตัวเลขบนการ์ดตรงกับที่นับเองจากหน้ารายการ และกราฟไม่ข้ามวันที่ยอดเป็นศูนย์</t>
         </is>
       </c>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="6" t="n"/>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>รอทดสอบ — จุดที่ต้องดู : ตัวเลขบนการ์ดตรงกับที่นับเองจากหน้ารายการหรือไม่ · ยอดอาหารที่ช่วยไว้ตรงกับจำนวนชุดของรายการที่รับแล้วหรือไม่ · กราฟ 7 วันไม่ข้ามวันที่ยอดเป็นศูนย์หรือไม่</t>
+        </is>
+      </c>
+      <c r="K20" s="11" t="inlineStr">
+        <is>
+          <t>รอทดสอบ</t>
+        </is>
+      </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
           <t>ผู้ทดสอบ: ผู้ดูแลระบบ | ยอดอาหารที่ช่วยไว้คือตัวชี้วัดหลักของโครงงาน</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="96" customHeight="1">
+    <row r="21" ht="170" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
           <t>SIT-053</t>
@@ -1710,15 +1892,23 @@
           <t>ผู้แจ้งได้รับแจ้งเตือนความคืบหน้า ร้านได้รับเฉพาะข้อความที่ผู้ดูแลตั้งใจส่ง และไม่เห็นบันทึกภายในหรือชื่อผู้แจ้ง</t>
         </is>
       </c>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="6" t="n"/>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>รอทดสอบ — จุดที่ต้องดู : แนบรูปหลักฐานแล้วผู้ดูแลเห็นหรือไม่ · ผู้แจ้งได้รับแจ้งเตือนความคืบหน้าหรือไม่ · ร้านได้รับเฉพาะข้อความที่ผู้ดูแลตั้งใจส่งหรือไม่ · ร้านเห็นบันทึกภายในหรือชื่อผู้แจ้งหรือไม่ (ต้องไม่เห็น)</t>
+        </is>
+      </c>
+      <c r="K21" s="11" t="inlineStr">
+        <is>
+          <t>รอทดสอบ</t>
+        </is>
+      </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
           <t>ผู้ทดสอบ: ผู้ดูแลระบบ | ตรวจให้แน่ว่าร้านไม่มีทางรู้ว่าใครแจ้ง</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="96" customHeight="1">
+    <row r="22" ht="170" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
           <t>SIT-052</t>
@@ -1767,8 +1957,16 @@
           <t>ร้านที่ถูกระงับหายจากหน้าลูกค้าและจองไม่ได้ พอปลดระงับแล้วเมนู โพสต์ และรีวิวเดิมยังอยู่ครบ</t>
         </is>
       </c>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="6" t="n"/>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>รอทดสอบ — จุดที่ต้องดู : ร้านที่ถูกระงับหายจากหน้าลูกค้าหรือไม่ · ลองจองอาหารของร้านนั้นแล้วระบบปฏิเสธหรือไม่ · ปลดระงับแล้วเมนู โพสต์ และรีวิวเดิมยังอยู่ครบหรือไม่</t>
+        </is>
+      </c>
+      <c r="K22" s="11" t="inlineStr">
+        <is>
+          <t>รอทดสอบ</t>
+        </is>
+      </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
           <t>ผู้ทดสอบ: ผู้ดูแลระบบ | ตรวจว่าการระงับไม่ได้ลบข้อมูลของร้าน</t>
@@ -1865,4 +2063,274 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>ผู้ทดสอบและการลงนามรับรองผล (UAT Sign-off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>เกณฑ์การยอมรับโดยรวม</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>ถือว่าระบบผ่านการยอมรับ เมื่อกรณีทดสอบทั้ง 21 ข้อมีสถานะ Pass และไม่มีข้อใดที่ผู้ทดสอบระบุว่าใช้งานจริงไม่ได้</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>กรณีที่ Fail ต้องบันทึกไว้ในช่อง Comments ว่าติดตรงไหน แล้วแก้ไขและทดสอบซ้ำก่อนส่งมอบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>ผู้ทดสอบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>บทบาท</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>ชื่อ-นามสกุล</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>ความเกี่ยวข้องกับโครงงาน</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>วันที่ทดสอบ</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>ลงชื่อ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>ลูกค้า</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr"/>
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>ลูกค้า</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr"/>
+      <c r="C10" s="7" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>เจ้าของร้าน</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr"/>
+      <c r="C11" s="7" t="inlineStr"/>
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>เจ้าของร้าน</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr"/>
+      <c r="C12" s="7" t="inlineStr"/>
+      <c r="D12" s="7" t="inlineStr"/>
+      <c r="E12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>ผู้ดูแลระบบ</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr"/>
+      <c r="C13" s="7" t="inlineStr"/>
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>สรุปผลการทดสอบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>หัวข้อ</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>จำนวน</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>กรณีทดสอบทั้งหมด</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>ผ่าน (Pass)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>ไม่ผ่าน (Fail)</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>สัดส่วนที่ผ่าน</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>ผู้รับรองผล</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>ตำแหน่ง</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>ชื่อ-นามสกุล</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>วันที่</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>ลงชื่อ</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>ตัวแทนกลุ่มผู้พัฒนา</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr"/>
+      <c r="C24" s="7" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>อาจารย์ที่ปรึกษา</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr"/>
+      <c r="C25" s="7" t="inlineStr"/>
+      <c r="D25" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>หมายเหตุ</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>ช่อง Actual Outcome และ Status ในชีต UAT ต้องกรอกจากการทดลองใช้จริงเท่านั้น ห้ามกรอกล่วงหน้า</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>ผู้ทดสอบควรเป็นคนที่ไม่ได้เขียนโค้ดส่วนนั้นเอง เพื่อให้เห็นจุดที่ผู้ใช้จริงสะดุด</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>ถ้าทดสอบบนระบบที่อยู่บนคลาวด์ ให้เปิดแอปทิ้งไว้ประมาณ 2 นาทีก่อนเริ่ม เพื่อปลุกเซิร์ฟเวอร์ให้ตื่นก่อน</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/G11_UAT.xlsx
+++ b/docs/G11_UAT.xlsx
@@ -3,15 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28800" yWindow="500" windowWidth="40960" windowHeight="16660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UAT" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="desc" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ผู้ทดสอบและการลงนาม" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="181029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -21,33 +20,29 @@
   <fonts count="6">
     <font>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="12"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="TH SarabunPSK"/>
-      <family val="2"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="TH SarabunPSK"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="TH SarabunPSK"/>
-      <family val="2"/>
       <color rgb="FF212529"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Aptos Narrow"/>
       <b val="1"/>
-      <sz val="13"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
@@ -63,17 +58,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
+        <fgColor rgb="00D5EAD3"/>
       </patternFill>
     </fill>
   </fills>
@@ -104,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -122,23 +116,14 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -259,108 +244,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -372,23 +263,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -398,23 +289,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -422,26 +313,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -476,17 +364,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -501,33 +389,8 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -538,24 +401,25 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10.796875" defaultRowHeight="18"/>
   <cols>
     <col width="14" customWidth="1" style="2" min="1" max="1"/>
     <col width="40" customWidth="1" style="2" min="2" max="2"/>
     <col width="22" customWidth="1" style="2" min="3" max="3"/>
-    <col width="14" customWidth="1" style="8" min="4" max="4"/>
-    <col width="44" customWidth="1" style="8" min="5" max="5"/>
-    <col width="20" customWidth="1" style="8" min="6" max="6"/>
-    <col width="46" customWidth="1" style="8" min="7" max="7"/>
-    <col width="46" customWidth="1" style="8" min="8" max="8"/>
-    <col width="46" customWidth="1" style="8" min="9" max="9"/>
-    <col width="52" customWidth="1" style="8" min="10" max="10"/>
-    <col width="18" customWidth="1" style="8" min="11" max="11"/>
-    <col width="34" customWidth="1" style="8" min="12" max="12"/>
-    <col width="10.83203125" customWidth="1" style="2" min="13" max="16384"/>
+    <col width="14" customWidth="1" style="7" min="4" max="4"/>
+    <col width="44" customWidth="1" style="7" min="5" max="5"/>
+    <col width="20" customWidth="1" style="7" min="6" max="6"/>
+    <col width="46" customWidth="1" style="7" min="7" max="9"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" style="7" min="10" max="10"/>
+    <col width="18" customWidth="1" style="7" min="11" max="11"/>
+    <col width="34" customWidth="1" style="7" min="12" max="12"/>
+    <col width="10.796875" customWidth="1" style="2" min="13" max="13"/>
+    <col width="10.796875" customWidth="1" style="2" min="14" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customFormat="1" customHeight="1" s="4">
+    <row r="1" ht="31.95" customFormat="1" customHeight="1" s="4">
       <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario ID</t>
@@ -617,43 +481,43 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="170" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+    <row r="2" ht="169.95" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>SIT-001</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>สมัครสมาชิกได้ และรหัสผ่านถูกเข้ารหัสก่อนเก็บ</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>RQ-001, RQ-004, RQ-005</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>UAT-001</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>ผู้ใช้ที่ไม่เคยใช้แอปมาก่อน สมัครสมาชิกเองได้จนจบโดยไม่ต้องมีคนสอน</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>RQ-001, RQ-004, RQ-005</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>ผู้ใช้ที่ไม่เคยใช้แอปมาก่อน สมัครสมาชิกเองได้จนจบโดยไม่ต้องมีคนสอน</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>1. เปิดแอปแล้วกดสมัครสมาชิก
 2. เลือกประเภทเป็นลูกค้า
@@ -661,128 +525,128 @@
 4. กดยืนยันการสมัคร</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>สมัครเสร็จแล้วเข้าใช้งานได้ทันที และถ้ากรอกผิดจะมีข้อความภาษาไทยบอกว่าผิดตรงไหน</t>
         </is>
       </c>
       <c r="J2" s="6" t="inlineStr">
         <is>
-          <t>ทดสอบบนมือถือจริง 10/09/2569 01:40 น. สมัครบัญชีลูกค้าใหม่ด้วยอีเมล patcharin.taraboon@gmail.com และเบอร์ 0622934006 สมัครจนจบได้เองโดยไม่ต้องมีคนแนะนำ เข้าใช้งานได้ทันทีหลังสมัคร และหน้าโปรไฟล์แสดงป้าย "บัญชีลูกค้า" พร้อมชื่อและเบอร์ที่กรอกไว้ถูกต้องครบทุกช่อง</t>
-        </is>
-      </c>
-      <c r="K2" s="12" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="L2" s="7" t="inlineStr">
-        <is>
-          <t>ผู้ทดสอบ: เจ้าของโครงงาน (บทบาทลูกค้า) | มีภาพหน้าจอประกอบ</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="170" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+          <t>ทดสอบสมัครสมาชิกในแอปสำเร็จ สามารถกรอกข้อมูลและสมัครบัญชีลูกค้าได้จนจบ แล้วเข้าใช้งานได้</t>
+        </is>
+      </c>
+      <c r="K2" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>ผู้ทดสอบ: ลูกค้า | สมัครสมาชิกสำเร็จและเข้าใช้งานได้ | ยังไม่ได้ทดสอบกรอกอีเมลผิดรูปแบบและข้อความแจ้งเตือนภาษาไทย</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="169.95" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>SIT-005</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>เข้าสู่ระบบด้วยอีเมลหรือเบอร์โทรก็ได้ ในช่องเดียวกัน</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>RQ-006</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>UAT-002</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>ผู้ใช้ที่จำอีเมลไม่ได้ ยังเข้าสู่ระบบได้ด้วยเบอร์โทรในช่องเดียวกัน</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>RQ-006</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>ผู้ใช้ที่จำอีเมลไม่ได้ ยังเข้าสู่ระบบได้ด้วยเบอร์โทรในช่องเดียวกัน</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>1. ออกจากระบบ
 2. กรอกเบอร์โทรในช่องแรกแทนอีเมล
 3. กรอกรหัสผ่านแล้วกดเข้าสู่ระบบ</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>เข้าสู่ระบบได้และเป็นบัญชีเดิม โดยผู้ใช้ไม่ต้องเลือกเองว่ากรอกอะไรลงไป</t>
         </is>
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
-          <t>ทดสอบบนมือถือจริง 10/09/2569 01:42 น. ออกจากระบบแล้วเข้าใหม่โดยกรอกเบอร์ 0622934006 ในช่องแรกแทนอีเมล เข้าสู่ระบบได้และเป็นบัญชีเดิม ผู้ใช้ไม่ต้องเลือกเองว่ากรอกอะไรลงไป ระบบแยกประเภทให้เอง</t>
-        </is>
-      </c>
-      <c r="K3" s="12" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="L3" s="7" t="inlineStr">
-        <is>
-          <t>ผู้ทดสอบ: เจ้าของโครงงาน (บทบาทลูกค้า) | มีภาพหน้าจอประกอบ</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="170" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+          <t>ทดสอบเข้าสู่ระบบด้วยหมายเลขโทรศัพท์ในช่องเดียวกับอีเมลสำเร็จ และเข้าสู่บัญชีเดิมได้</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>ผู้ทดสอบ: ลูกค้า | เข้าสู่ระบบด้วยเบอร์โทรศัพท์สำเร็จ | ยังไม่ได้ทดสอบความเข้าใจของผู้ใช้ว่าช่องนี้รองรับทั้งอีเมลและเบอร์โทร</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="169.95" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>SIT-007</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>ขอตั้งรหัสผ่านใหม่ได้ และรหัสยืนยันใช้ได้ครั้งเดียว</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>RQ-009, RQ-010</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>UAT-003</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>ผู้ใช้ที่ลืมรหัสผ่าน กู้บัญชีคืนได้เองโดยไม่ต้องติดต่อใคร</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>RQ-009, RQ-010</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>ผู้ใช้ที่ลืมรหัสผ่าน กู้บัญชีคืนได้เองโดยไม่ต้องติดต่อใคร</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>1. กดลืมรหัสผ่านที่หน้าเข้าสู่ระบบ
 2. กรอกอีเมลที่ลงทะเบียนไว้
@@ -790,128 +654,128 @@
 4. ตั้งรหัสผ่านใหม่แล้วเข้าสู่ระบบ</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" s="1" t="inlineStr">
         <is>
           <t>ตั้งรหัสผ่านใหม่สำเร็จและเข้าสู่ระบบได้ รหัสเดิมใช้ไม่ได้อีก</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>ทดสอบจริง 10/09/2569 01:43 น. ขอตั้งรหัสผ่านใหม่ ระบบออกรหัส 6 หลักและลิงก์ให้พร้อมกัน ตั้งรหัสใหม่สำเร็จและกลับเข้าสู่ระบบด้วยรหัสใหม่ได้ ข้อสังเกต : เซิร์ฟเวอร์ยังไม่ได้ตั้งค่า SMTP อีเมลจึงไม่ถูกส่งออกจริง ระบบรองรับกรณีนี้ไว้แล้วโดยแสดงกล่อง "โหมดสาธิต" พร้อมกรอกรหัส 6 หลักให้อัตโนมัติในแอป ผู้ทดสอบเลือกใช้เส้นทางลิงก์ผ่านเบราว์เซอร์แทน จึงต้องเปิดดูรหัสจาก Log ของ Render</t>
-        </is>
-      </c>
-      <c r="K4" s="12" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>ผู้ทดสอบ: เจ้าของโครงงาน (บทบาทลูกค้า) | มีภาพหน้าจอประกอบ | *** ก่อนใช้งานจริงต้องตั้งค่า SMTP บน Render ไม่งั้นผู้ใช้จริงจะไม่ได้รับอีเมล ***</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="170" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+          <t>ทดสอบตั้งรหัสผ่านใหม่สำเร็จ โดยใช้รหัสยืนยัน 6 หลักจาก Render logs แล้วระบบแสดงหน้าตั้งรหัสผ่านใหม่เรียบร้อย</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t>ผู้ทดสอบ: ลูกค้า | ตั้งรหัสผ่านใหม่สำเร็จ | ข้อจำกัด: SMTP ยังไม่ตั้งค่า จึงไม่ได้รับรหัสทางอีเมล ต้องดูรหัสยืนยัน 6 หลักจาก Render logs | ยังไม่ได้ทดสอบว่ารหัสเดิมใช้เข้าสู่ระบบไม่ได้</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="169.95" customHeight="1">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>SIT-028</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>ค้นหาและเรียงลำดับอาหารทำงานถูกต้อง</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>RQ-026, RQ-027, RQ-028</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>UAT-004</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>ผู้ใช้หาอาหารที่อยากได้เจอ โดยไม่ต้องเลื่อนดูทั้งหมด</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>RQ-026, RQ-027, RQ-028</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>ผู้ใช้หาอาหารที่อยากได้เจอ โดยไม่ต้องเลื่อนดูทั้งหมด</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="1" t="inlineStr">
         <is>
           <t>1. พิมพ์ชื่ออาหารที่ต้องการในช่องค้นหา
 2. เปิดตัวกรอง เลือกหมวดหมู่และช่วงราคา
 3. เปลี่ยนการเรียงลำดับเป็นราคาน้อยไปมาก</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="1" t="inlineStr">
         <is>
           <t>ผลลัพธ์ตรงกับสิ่งที่กรอง และเรียงลำดับถูกต้องตามที่เลือก</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>รอทดสอบ — จุดที่ต้องดู : ผลค้นหาตรงกับคำที่พิมพ์หรือไม่ · กรองหมวดหมู่และช่วงราคาแล้วผลลัพธ์เปลี่ยนถูกต้องหรือไม่ · เรียงราคาน้อยไปมากแล้วเรียงถูกจริงหรือไม่ · ผู้ใช้บอกว่าตัวกรองขาดอะไร</t>
-        </is>
-      </c>
-      <c r="K5" s="11" t="inlineStr">
-        <is>
-          <t>รอทดสอบ</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>ผู้ทดสอบ: ลูกค้า | ถามว่าตัวกรองที่มีเพียงพอไหม ขาดอะไร</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="170" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+          <t>ทดสอบค้นหาอาหารและใช้ตัวกรองสำเร็จ พบผลลัพธ์ตรงกับคำค้น เช่น “น้ำ” และ “ขนม” เลือกหมวดหมู่เบเกอรี่ได้ และเรียงลำดับรายการได้</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L5" s="1" t="inlineStr">
+        <is>
+          <t>ผู้ทดสอบ: ลูกค้า | ค้นหาอาหารได้ตรงคำค้น ใช้ตัวกรองหมวดหมู่และตัวเลือกเรียงลำดับได้</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="169.95" customHeight="1">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>SIT-026</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>ค้นหาร้านตามระยะทางได้ถูกต้อง และไม่มีร้านไกลเกินปนมา</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>RQ-029, RQ-030</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t>UAT-005</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="1" t="inlineStr">
         <is>
           <t>ผู้ใช้ดูได้ว่ามีร้านไหนอยู่ใกล้ตัว และไกลแค่ไหน</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="1" t="inlineStr">
         <is>
           <t>RQ-029, RQ-030, RQ-031</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>ผู้ใช้ดูได้ว่ามีร้านไหนอยู่ใกล้ตัว และไกลแค่ไหน</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="1" t="inlineStr">
         <is>
           <t>1. เปิดแท็บแผนที่แล้วอนุญาตให้เข้าถึงตำแหน่ง
 2. ดูหมุดร้านและระยะทางที่แสดง
@@ -919,64 +783,64 @@
 4. ลองปฏิเสธสิทธิ์ตำแหน่งแล้วดูว่ายังใช้งานต่อได้</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="1" t="inlineStr">
         <is>
           <t>เห็นร้านใกล้ตัวพร้อมระยะทางเป็นกิโลเมตร และเมื่อไม่ให้สิทธิ์ตำแหน่งก็ยังดูรายการร้านได้</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>รอทดสอบ — จุดที่ต้องดู : เห็นหมุดร้านพร้อมระยะทางเป็นกิโลเมตรหรือไม่ · เปลี่ยนรัศมีเป็น 1 กม. แล้วร้านลดลงหรือไม่ · ปฏิเสธสิทธิ์ตำแหน่งแล้วยังดูรายการร้านได้หรือไม่ · ระยะทางที่แสดงใกล้เคียงความจริงหรือไม่</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>รอทดสอบ</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>ผู้ทดสอบ: ลูกค้า | ตรวจว่าระยะทางที่แสดงใกล้เคียงความจริง</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="170" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+          <t>ทดสอบค้นหาร้านตามระยะทางสำเร็จ: เลือกรัศมี 5 กม. พบ 2 ร้านที่ระยะ 730 ม. และ 3.7 กม. เมื่อเปลี่ยนเป็น 1 กม. เหลือเฉพาะร้านที่ระยะ 730 ม. ไม่มีร้านไกลเกินรัศมีปนมา</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>ผู้ทดสอบ: ลูกค้า | ระยะทางและการกรองตามรัศมี 1 กม. และ 5 กม. แสดงผลถูกต้อง</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="169.95" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>SIT-014</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>จองสำเร็จแล้วจำนวนอาหารลดลงทันทีในขั้นตอนเดียวกัน</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>RQ-033, RQ-034, RQ-035, RQ-036</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>UAT-006</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="1" t="inlineStr">
         <is>
           <t>ผู้ใช้จองอาหารได้ และรู้ว่าต้องเอาอะไรไปแสดงที่ร้าน</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>RQ-033, RQ-035, RQ-036</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>ผู้ใช้จองอาหารได้ และรู้ว่าต้องเอาอะไรไปแสดงที่ร้าน</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="1" t="inlineStr">
         <is>
           <t>1. เลือกรายการอาหารที่ต้องการ
 2. เลือกจำนวนแล้วกดยืนยันการจอง
@@ -984,64 +848,64 @@
 4. ปิดแอปแล้วเปิดใหม่ กลับมาดู QR อีกครั้ง</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="1" t="inlineStr">
         <is>
           <t>จองสำเร็จ เห็น QR Code กับรหัส 4 หลัก และเปิดดูซ้ำได้ตลอดเวลาที่คิวยังไม่หมดอายุ</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>[ตรวจระดับ API 10/09/2569 01:03] จองสำเร็จ ได้ reservation_id 4 และรหัสรับ 1898 จำนวนคงเหลือของโพสต์ลดจาก 3 เหลือ 2 ทันที และ expires_at ถูกตั้งเป็น 01:15:15 ตรงตาม hold_minutes 12 นาทีที่ร้านกำหนด — ยังไม่ได้ตรวจการแสดง QR บนหน้าจอ  ยังต้องดูบนหน้าจอ : QR Code แสดงผลถูกต้อง และเปิดดูซ้ำได้หลังปิด-เปิดแอป</t>
-        </is>
-      </c>
-      <c r="K7" s="11" t="inlineStr">
-        <is>
-          <t>รอยืนยันบนแอป</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>ผู้ทดสอบ: ลูกค้า | ถามว่าเข้าใจไหมว่าต้องทำอะไรต่อ  ||  ตรวจด้วยสคริปต์ยิง API จริงเข้า https://saveeats.onrender.com ด้วยบัญชี seed (customer1@test.com / seller1@test.com) ยังไม่ใช่การทดสอบโดยผู้ใช้บนหน้าจอ ต้องเปิดแอปยืนยันด้วยตาแล้วจึงกรอกช่อง Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="170" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+          <t>ทดสอบจองเค้กสำเร็จ: จำนวนคงเหลือลดจาก 7 ชุดเป็น 6 ชุดทันทีหลังจอง และหน้าจอแสดง QR Code กับรหัสรับอาหาร 4 หลัก</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
+          <t>ผู้ทดสอบ: ลูกค้า | ยืนยันจำนวนอาหารลดลงทันทีหลังจอง พร้อมแสดง QR Code และรหัสรับอาหาร</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="169.95" customHeight="1">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>SIT-017</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>เวลาหมดอายุของคิวคำนวณตามกฎที่ระบบกำหนด</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>RQ-035, RQ-038</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>UAT-007</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="1" t="inlineStr">
         <is>
           <t>ผู้ใช้รู้ตัวก่อนคิวหมดเวลา จึงไปรับทันหรือยกเลิกคืนของให้คนอื่นได้</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>RQ-038, RQ-045</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>ผู้ใช้รู้ตัวก่อนคิวหมดเวลา จึงไปรับทันหรือยกเลิกคืนของให้คนอื่นได้</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="1" t="inlineStr">
         <is>
           <t>1. จองอาหารจากโพสต์ที่ตั้งเวลาถือคิวไว้สั้น ๆ
 2. ดูตัวนับถอยหลังในหน้ารายละเอียดการจอง
@@ -1049,256 +913,256 @@
 4. เปิดหน้าการแจ้งเตือน</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="1" t="inlineStr">
         <is>
           <t>เห็นเวลานับถอยหลังชัดเจน และได้รับข้อความเตือนก่อนหมดเวลา 1 ครั้ง ไม่ถูกเตือนซ้ำ ๆ</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>[ตรวจระดับ API 10/09/2569 01:03-01:22] จองเวลา 01:03:52 คิวหมดอายุ 01:15:52 ระบบส่งข้อความ "ใกล้หมดเวลารับอาหาร — เหลืออีกประมาณ 10 นาที" เมื่อ 01:05:41 งานเบื้องหลังวิ่งอีก 3 รอบหลังจากนั้น (01:10 / 01:15 / 01:20) ยังคงมีข้อความเตือนเพียง 1 ฉบับ ไม่มีการเตือนซ้ำ — ยังไม่ได้ตรวจตัวนับถอยหลังบนหน้าจอ  ยังต้องดูบนหน้าจอ : ตัวนับถอยหลังเดินถูกต้อง และข้อความเตือนโผล่ในหน้าการแจ้งเตือนของลูกค้า</t>
-        </is>
-      </c>
-      <c r="K8" s="11" t="inlineStr">
-        <is>
-          <t>รอยืนยันบนแอป</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>ผู้ทดสอบ: ลูกค้า | ข้อนี้ครอบคลุม RQ-045 ที่เพิ่งพัฒนาเสร็จ  ||  ตรวจด้วยสคริปต์ยิง API จริงเข้า https://saveeats.onrender.com ด้วยบัญชี seed (customer1@test.com / seller1@test.com) ยังไม่ใช่การทดสอบโดยผู้ใช้บนหน้าจอ ต้องเปิดแอปยืนยันด้วยตาแล้วจึงกรอกช่อง Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="170" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+          <t>ทดสอบการแจ้งเตือนใกล้หมดเวลารับอาหารสำเร็จ ระบบแสดงข้อความ “ใกล้หมดเวลารับอาหาร” และแจ้งว่าเหลืออีกประมาณ 11 นาที</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t>ผู้ทดสอบ: ลูกค้า | พบการแจ้งเตือนใกล้หมดเวลารับอาหารในหน้าการแจ้งเตือน | ยังไม่ได้ทดสอบการแจ้งเตือนซ้ำหลายครั้ง</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="169.95" customHeight="1">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>SIT-018</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>ยกเลิกการจองแล้วของกลับเข้าระบบทันที</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>RQ-039</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="1" t="inlineStr">
         <is>
           <t>UAT-008</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="1" t="inlineStr">
         <is>
           <t>ผู้ใช้ที่ไปรับไม่ทัน ยกเลิกเองได้ และของกลับไปให้คนอื่นซื้อต่อ</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="1" t="inlineStr">
         <is>
           <t>RQ-039</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>ผู้ใช้ที่ไปรับไม่ทัน ยกเลิกเองได้ และของกลับไปให้คนอื่นซื้อต่อ</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="1" t="inlineStr">
         <is>
           <t>1. เปิดรายการจองที่ยังไม่ได้ไปรับ
 2. กดยกเลิกการจองแล้วยืนยัน
 3. กลับไปดูรายการอาหารรายการเดิมในหน้าแรก</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="1" t="inlineStr">
         <is>
           <t>ยกเลิกสำเร็จ และจำนวนคงเหลือของรายการนั้นเพิ่มกลับมาให้คนอื่นจองต่อได้</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>[ตรวจระดับ API 10/09/2569 01:03] ลูกค้ายกเลิกเอง สถานะเปลี่ยนเป็น cancelled และจำนวนคงเหลือของโพสต์กลับจาก 2 เป็น 3 ทันทีในคำขอเดียวกัน  ยังต้องดูบนหน้าจอ : ข้อความเตือนก่อนกดยกเลิกอ่านแล้วเข้าใจ และรายการหายจากหน้าการจอง</t>
-        </is>
-      </c>
-      <c r="K9" s="11" t="inlineStr">
-        <is>
-          <t>รอยืนยันบนแอป</t>
-        </is>
-      </c>
-      <c r="L9" s="7" t="inlineStr">
-        <is>
-          <t>ผู้ทดสอบ: ลูกค้า | สังเกตว่าข้อความเตือนก่อนยกเลิกชัดพอไหม  ||  ตรวจด้วยสคริปต์ยิง API จริงเข้า https://saveeats.onrender.com ด้วยบัญชี seed (customer1@test.com / seller1@test.com) ยังไม่ใช่การทดสอบโดยผู้ใช้บนหน้าจอ ต้องเปิดแอปยืนยันด้วยตาแล้วจึงกรอกช่อง Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="170" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+          <t>ทดสอบยกเลิกการจองสำเร็จ รายการน้ำลำไยแสดงสถานะ “ยกเลิก” และจำนวนคงเหลือกลับเข้าระบบจาก 5 ชุดเป็น 6 ชุด</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L9" s="1" t="inlineStr">
+        <is>
+          <t>ผู้ทดสอบ: ลูกค้า | ยกเลิกการจองสำเร็จ และตรวจพบจำนวนอาหารกลับเข้าระบบทันที</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="169.95" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>SIT-046</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>เขียนรีวิวได้เฉพาะการจองที่รับอาหารแล้ว</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>RQ-062</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="1" t="inlineStr">
         <is>
           <t>UAT-009</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="1" t="inlineStr">
         <is>
           <t>ผู้ใช้ให้คะแนนร้านได้หลังรับอาหารจริง และคะแนนไปปรากฏที่หน้าร้าน</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="1" t="inlineStr">
         <is>
           <t>RQ-062, RQ-063</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>ผู้ใช้ให้คะแนนร้านได้หลังรับอาหารจริง และคะแนนไปปรากฏที่หน้าร้าน</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="1" t="inlineStr">
         <is>
           <t>1. รับอาหารที่ร้านจนสถานะเป็นรับแล้ว
 2. กดเขียนรีวิว ให้ดาวและพิมพ์ความเห็น
 3. เปิดหน้าร้านนั้นดูคะแนนเฉลี่ยและจำนวนรีวิว</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" s="1" t="inlineStr">
         <is>
           <t>รีวิวถูกบันทึก คะแนนเฉลี่ยของร้านเปลี่ยนตาม และรีวิวการจองเดิมซ้ำอีกครั้งไม่ได้</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>รอทดสอบ — จุดที่ต้องดู : เขียนรีวิวได้เฉพาะการจองที่รับอาหารแล้วหรือไม่ · คะแนนเฉลี่ยของร้านเปลี่ยนตามทันทีหรือไม่ · รีวิวการจองเดิมซ้ำแล้วระบบปฏิเสธหรือไม่ · คะแนนที่เห็นตรงกันทุกหน้าจอหรือไม่</t>
-        </is>
-      </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>รอทดสอบ</t>
-        </is>
-      </c>
-      <c r="L10" s="7" t="inlineStr">
-        <is>
-          <t>ผู้ทดสอบ: ลูกค้า | ตรวจว่าคะแนนที่เห็นตรงกันทุกหน้าจอ</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="170" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+          <t>ทดสอบรีวิวหลังรับอาหารสำเร็จ: รายการจองเค้กช็อกโกแลตแสดงสถานะ “รับอาหารแล้ว” จึงมีปุ่มเขียนรีวิว ส่งคะแนน 5 ดาวพร้อมข้อความ “อร่อยมากแม่” แล้วคะแนนเฉลี่ยร้านแสดง 5.0 จาก 1 รีวิว</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L10" s="1" t="inlineStr">
+        <is>
+          <t>ผู้ทดสอบ: ลูกค้า | เขียนรีวิวได้เฉพาะรายการที่รับอาหารแล้ว และคะแนน/ข้อความรีวิวปรากฏในหน้าร้าน | ยังไม่ได้ทดสอบการส่งรีวิวซ้ำของรายการเดิม</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="169.95" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>SIT-008</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>ร้านที่ยังไม่ได้รับอนุมัติต้องไม่แสดงให้ลูกค้าเห็น</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>RQ-014, RQ-015</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t>UAT-010</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="1" t="inlineStr">
         <is>
           <t>เจ้าของร้านลงทะเบียนร้านเองได้ และเข้าใจว่าต้องรออนุมัติก่อนขาย</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="1" t="inlineStr">
         <is>
           <t>RQ-014, RQ-015, RQ-016</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>เจ้าของร้านลงทะเบียนร้านเองได้ และเข้าใจว่าต้องรออนุมัติก่อนขาย</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>1. สมัครสมาชิกโดยเลือกประเภทร้านค้า
 2. กรอกชื่อร้าน ที่อยู่ เบอร์ติดต่อ และปักหมุดตำแหน่ง
 3. เข้าหน้าแรกของร้าน ดูสถานะที่แสดง</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>ลงทะเบียนสำเร็จ ร้านขึ้นสถานะรออนุมัติ พร้อมข้อความอธิบายว่ายังลงขายไม่ได้และต้องรออะไร</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>รอทดสอบ — จุดที่ต้องดู : ลงทะเบียนร้านจนจบได้หรือไม่ · ปักหมุดตำแหน่งได้หรือไม่ · หน้าแรกขึ้นสถานะรออนุมัติพร้อมคำอธิบายหรือไม่ · เจ้าของร้านเข้าใจไหมว่าทำไมยังขายไม่ได้</t>
-        </is>
-      </c>
-      <c r="K11" s="11" t="inlineStr">
-        <is>
-          <t>รอทดสอบ</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="inlineStr">
-        <is>
-          <t>ผู้ทดสอบ: เจ้าของร้าน | ถามว่าเข้าใจไหมว่าทำไมยังขายไม่ได้</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="170" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+          <t>ทดสอบสมัครร้านค้าสำเร็จ ร้านขึ้นสถานะ “รออนุมัติ” พร้อมข้อความว่าผู้ดูแลระบบกำลังตรวจสอบ และมีการแจ้งเตือนว่าส่งคำขอเปิดร้านแล้ว</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L11" s="1" t="inlineStr">
+        <is>
+          <t>ผู้ทดสอบ: เจ้าของร้าน | ยืนยันว่าร้านใหม่ปรากฏในหน้าร้านรออนุมัติของผู้ดูแลระบบ และร้านยังไม่สามารถลงขายได้ระหว่างรออนุมัติ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="169.95" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>SIT-011</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>สร้างประกาศขายอาหาร และระบบคิดส่วนลดให้เองที่เซิร์ฟเวอร์</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>RQ-020, RQ-022</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="1" t="inlineStr">
         <is>
           <t>UAT-011</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="1" t="inlineStr">
         <is>
           <t>เจ้าของร้านลงขายอาหารที่เหลือได้ภายในไม่กี่นาที และไม่ต้องคิดส่วนลดเอง</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="1" t="inlineStr">
         <is>
           <t>RQ-020, RQ-021, RQ-022</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>เจ้าของร้านลงขายอาหารที่เหลือได้ภายในไม่กี่นาที และไม่ต้องคิดส่วนลดเอง</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="1" t="inlineStr">
         <is>
           <t>1. เพิ่มเมนูใหม่เข้าคลังเมนู
 2. สร้างโพสต์ขาย เลือกเมนู ใส่ราคาเดิมกับราคาลด และจำนวน
@@ -1306,128 +1170,128 @@
 4. เปิดแอปฝั่งลูกค้าดูว่าโพสต์ขึ้นแล้ว</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" s="1" t="inlineStr">
         <is>
           <t>โพสต์ขึ้นให้ลูกค้าเห็น ระบบคิดเปอร์เซ็นต์ส่วนลดให้เอง และข้อมูลตรงกับที่ร้านกรอกทุกช่อง</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>รอทดสอบ — จุดที่ต้องดู : เพิ่มเมนูแล้วลงขายได้หรือไม่ · ระบบคิดเปอร์เซ็นต์ส่วนลดให้เองถูกต้องหรือไม่ · แนบรูปแล้วรูปขึ้นฝั่งลูกค้าหรือไม่ · ข้อมูลตรงกับที่ร้านกรอกครบทุกช่องหรือไม่ · ใช้เวลากี่นาทีตั้งแต่เริ่มจนโพสต์ขึ้น</t>
-        </is>
-      </c>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
-          <t>รอทดสอบ</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>ผู้ทดสอบ: เจ้าของร้าน | จับเวลาตั้งแต่เริ่มจนโพสต์ขึ้น</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="170" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+          <t>ทดสอบสร้างโพสต์ขายสำเร็จ: เพิ่มเมนูน้ำแตงโมปั่น ราคาเดิม 35 บาท ราคาขาย 18 บาท จำนวน 4 ชุด ระบบคำนวณส่วนลดอัตโนมัติเป็น 49% และโพสต์แสดงฝั่งลูกค้าพร้อมรูป ราคา และจำนวนคงเหลือ 4 ชุด</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L12" s="1" t="inlineStr">
+        <is>
+          <t>ผู้ทดสอบ: เจ้าของร้าน | ระบบคำนวณส่วนลดจาก 35 เป็น 18 บาทได้ 49% และข้อมูลโพสต์ตรงกันทั้งฝั่งร้านและลูกค้า</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="169.95" customHeight="1">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>SIT-036</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>ร้านได้รับแจ้งเตือนเมื่อมีการจองใหม่</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>RQ-046</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="1" t="inlineStr">
         <is>
           <t>UAT-012</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="1" t="inlineStr">
         <is>
           <t>เจ้าของร้านรู้ทันทีเมื่อมีลูกค้าจองเข้ามา โดยไม่ต้องคอยเปิดดูเอง</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="1" t="inlineStr">
         <is>
           <t>RQ-046</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>เจ้าของร้านรู้ทันทีเมื่อมีลูกค้าจองเข้ามา โดยไม่ต้องคอยเปิดดูเอง</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="1" t="inlineStr">
         <is>
           <t>1. ให้ลูกค้าจองอาหารของร้านนี้
 2. ดูจุดแดงบนกระดิ่งที่หน้าแรกของร้าน
 3. กดกระดิ่งเปิดหน้าการแจ้งเตือน</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="1" t="inlineStr">
         <is>
           <t>มีจุดแดงขึ้นบนกระดิ่ง และในหน้าการแจ้งเตือนมีข้อความว่ามีการจองใหม่ พร้อมชื่ออาหาร</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>[ตรวจระดับ API 10/09/2569 01:03:16] ร้านได้รับข้อความ "มีการจองใหม่ — มีลูกค้าจอง ข้าวกะเพราหมูสับไข่ดาว จากร้านของคุณ" ภายในไม่กี่วินาทีหลังลูกค้ากดจอง — ยังไม่ได้ตรวจจุดแดงบนกระดิ่งในแอป  ยังต้องดูบนหน้าจอ : จุดแดงขึ้นบนกระดิ่งที่หน้าแรกของร้าน และกดเข้าไปอ่านข้อความได้</t>
-        </is>
-      </c>
-      <c r="K13" s="11" t="inlineStr">
-        <is>
-          <t>รอยืนยันบนแอป</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>ผู้ทดสอบ: เจ้าของร้าน | ถามว่าเห็นจุดแดงเร็วพอที่จะเตรียมของทันไหม  ||  ตรวจด้วยสคริปต์ยิง API จริงเข้า https://saveeats.onrender.com ด้วยบัญชี seed (customer1@test.com / seller1@test.com) ยังไม่ใช่การทดสอบโดยผู้ใช้บนหน้าจอ ต้องเปิดแอปยืนยันด้วยตาแล้วจึงกรอกช่อง Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="170" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+          <t>ทดสอบแจ้งเตือนร้านเมื่อมีการจองใหม่สำเร็จ หลังลูกค้าจอง ระบบขึ้นจุดแดงบนกระดิ่งของร้าน และหน้าแจ้งเตือนแสดงข้อความ “มีการจองใหม่” พร้อมชื่ออาหาร</t>
+        </is>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L13" s="1" t="inlineStr">
+        <is>
+          <t>ผู้ทดสอบ: เจ้าของร้าน | ร้านได้รับการแจ้งเตือนการจองใหม่และเปิดอ่านข้อความในหน้าการแจ้งเตือนได้</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="169.95" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>SIT-018</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>ยกเลิกการจองแล้วของกลับเข้าระบบทันที</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>RQ-039</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="1" t="inlineStr">
         <is>
           <t>UAT-013</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="1" t="inlineStr">
         <is>
           <t>เจ้าของร้านรู้เมื่อลูกค้ายกเลิก จะได้เอาของไปขายต่อในเวลาที่ยังเหลือ</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="1" t="inlineStr">
         <is>
           <t>RQ-046</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>เจ้าของร้านรู้เมื่อลูกค้ายกเลิก จะได้เอาของไปขายต่อในเวลาที่ยังเหลือ</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="1" t="inlineStr">
         <is>
           <t>1. ให้ลูกค้าจองอาหารของร้านนี้
 2. ให้ลูกค้ากดยกเลิกการจองเอง
@@ -1435,64 +1299,64 @@
 4. ดูจำนวนคงเหลือของโพสต์นั้น</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="1" t="inlineStr">
         <is>
           <t>ร้านได้รับข้อความว่าลูกค้ายกเลิกการจอง และจำนวนคงเหลือกลับมาให้ขายต่อได้</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>[ตรวจระดับ API 10/09/2569 01:03:32] ลูกค้ากดยกเลิก ร้านได้รับข้อความ "ลูกค้ายกเลิกการจอง — ลูกค้ายกเลิกการจอง ข้าวกะเพราหมูสับไข่ดาว ของถูกคืนเข้าระบบให้ขายต่อแล้ว" และจำนวนคงเหลือกลับมาเป็น 3 — ยังไม่ได้ตรวจการเปิดอ่านผ่านกระดิ่งในแอป  ยังต้องดูบนหน้าจอ : ร้านกดกระดิ่งแล้วเห็นข้อความ "ลูกค้ายกเลิกการจอง"</t>
-        </is>
-      </c>
-      <c r="K14" s="11" t="inlineStr">
-        <is>
-          <t>รอยืนยันบนแอป</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="inlineStr">
-        <is>
-          <t>ผู้ทดสอบ: เจ้าของร้าน | ข้อนี้คือครึ่งหลังของ RQ-046 ที่เพิ่งพัฒนาเสร็จ  ||  ตรวจด้วยสคริปต์ยิง API จริงเข้า https://saveeats.onrender.com ด้วยบัญชี seed (customer1@test.com / seller1@test.com) ยังไม่ใช่การทดสอบโดยผู้ใช้บนหน้าจอ ต้องเปิดแอปยืนยันด้วยตาแล้วจึงกรอกช่อง Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="170" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+          <t>ทดสอบการยกเลิกการจองฝั่งร้านสำเร็จ: ลูกค้ายกเลิกการจองครัวซองต์เนยสด อาหารกลับเข้าระบบให้ขายต่อ และร้านได้รับการแจ้งเตือนข้อความ “ลูกค้ายกเลิกการจอง”</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L14" s="1" t="inlineStr">
+        <is>
+          <t>ผู้ทดสอบ: เจ้าของร้าน | ร้านได้รับแจ้งเตือนการยกเลิกทันที และตรวจพบรายการอาหารกลับมาให้ลูกค้าจองต่อได้</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="169.95" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>SIT-021</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>ร้านสแกนรับอาหารแล้ว สถานะเปลี่ยนตรงกันทั้งสองฝั่ง</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>RQ-040</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="1" t="inlineStr">
         <is>
           <t>UAT-014</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="1" t="inlineStr">
         <is>
           <t>เจ้าของร้านยืนยันการส่งมอบอาหารได้เร็ว ไม่ทำให้ลูกค้ารอหน้าร้าน</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="1" t="inlineStr">
         <is>
           <t>RQ-040</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>เจ้าของร้านยืนยันการส่งมอบอาหารได้เร็ว ไม่ทำให้ลูกค้ารอหน้าร้าน</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="1" t="inlineStr">
         <is>
           <t>1. ให้ลูกค้าเปิด QR Code ที่หน้าจอ
 2. กดสแกน QR จากแอปของร้าน
@@ -1500,256 +1364,256 @@
 4. ดูสถานะการจองทั้งฝั่งร้านและฝั่งลูกค้า</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I15" s="1" t="inlineStr">
         <is>
           <t>ยืนยันสำเร็จภายในไม่กี่วินาที และสถานะเปลี่ยนเป็นรับอาหารแล้วตรงกันทั้งสองฝั่ง</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>รอทดสอบ — จุดที่ต้องดู : สแกน QR แล้วสถานะเปลี่ยนภายในกี่วินาที · สแกนไม่ได้แล้วกรอกรหัส 4 หลักแทนได้หรือไม่ · สถานะเปลี่ยนตรงกันทั้งฝั่งร้านและฝั่งลูกค้าหรือไม่ · ทดสอบในที่แสงน้อยแล้วยังสแกนติดหรือไม่</t>
-        </is>
-      </c>
-      <c r="K15" s="11" t="inlineStr">
-        <is>
-          <t>รอทดสอบ</t>
-        </is>
-      </c>
-      <c r="L15" s="7" t="inlineStr">
-        <is>
-          <t>ผู้ทดสอบ: เจ้าของร้าน | ทดสอบในที่แสงน้อยด้วย เพราะหน้าร้านจริงตอนเย็นมืด</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="170" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+          <t>ทดสอบร้านยืนยันการรับอาหารสำเร็จ: ร้านกรอกรหัส 4 หลัก 4909 ที่ลูกค้าแสดง แล้วระบบยืนยันสำเร็จ สถานะรายการข้าวกะเพราหมูกรอบเปลี่ยนเป็น “รับอาหารแล้ว” ทั้งหน้าร้านและหน้าการจองของลูกค้า</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L15" s="1" t="inlineStr">
+        <is>
+          <t>ผู้ทดสอบ: เจ้าของร้านและลูกค้า | ยืนยันการรับอาหารด้วยรหัส 4 หลักสำเร็จ และตรวจพบสถานะตรงกันทั้งสองฝั่ง</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="169.95" customHeight="1">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>SIT-022</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr">
         <is>
           <t>สแกนรหัสเดิมซ้ำครั้งที่สอง ต้องถูกปฏิเสธ</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>RQ-041</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="1" t="inlineStr">
         <is>
           <t>UAT-015</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="1" t="inlineStr">
         <is>
           <t>ระบบกันไม่ให้รับอาหารซ้ำหรือรับของร้านอื่น โดยบอกเหตุผลให้ร้านเข้าใจ</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F16" s="1" t="inlineStr">
         <is>
           <t>RQ-041</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>ระบบกันไม่ให้รับอาหารซ้ำหรือรับของร้านอื่น โดยบอกเหตุผลให้ร้านเข้าใจ</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="1" t="inlineStr">
         <is>
           <t>1. สแกน QR ที่เพิ่งใช้ไปแล้วอีกครั้ง
 2. ให้ร้านอื่นลองสแกน QR ใบเดียวกัน
 3. สแกน QR ของคิวที่เลยเวลารับไปแล้ว</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="1" t="inlineStr">
         <is>
           <t>ทั้ง 3 กรณีถูกปฏิเสธ และขึ้นข้อความภาษาไทยที่บอกชัดว่าเป็นเพราะอะไร ไม่ใช่ข้อความรวม ๆ</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>รอทดสอบ — จุดที่ต้องดู : สแกน QR ที่ใช้ไปแล้วถูกปฏิเสธหรือไม่ · ร้านอื่นสแกน QR ใบเดียวกันถูกปฏิเสธหรือไม่ · สแกนคิวที่หมดเวลาถูกปฏิเสธหรือไม่ · ข้อความที่ขึ้นบอกเหตุผลต่างกันทั้ง 3 กรณีหรือไม่ · อ่านแล้วรู้ไหมว่าต้องทำอะไรต่อ</t>
-        </is>
-      </c>
-      <c r="K16" s="11" t="inlineStr">
-        <is>
-          <t>รอทดสอบ</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>ผู้ทดสอบ: เจ้าของร้าน | ถามว่าอ่านข้อความแล้วรู้ไหมว่าต้องทำอะไรต่อ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="170" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+          <t>ทดสอบใช้รหัสรับอาหารซ้ำสำเร็จ: หลังรายการข้าวกะเพราหมูกรอบรหัส 4909 มีสถานะ “รับอาหารแล้ว” ร้านกรอกรหัสเดิมเพื่อยืนยันอีกครั้ง ระบบปฏิเสธและแสดงข้อความ “ยืนยันไม่สำเร็จ — ไม่พบการจองนี้ในระบบ”</t>
+        </is>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L16" s="1" t="inlineStr">
+        <is>
+          <t>ผู้ทดสอบ: เจ้าของร้าน | ระบบป้องกันการยืนยันรับอาหารซ้ำด้วยรหัสเดิม และแสดงข้อความปฏิเสธชัดเจน</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="169.95" customHeight="1">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>SIT-037</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>ระบบยกเลิกคิวที่หมดเวลาและคืนของให้เองอัตโนมัติ</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>RQ-042</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="1" t="inlineStr">
         <is>
           <t>UAT-016</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="1" t="inlineStr">
         <is>
           <t>ของที่ลูกค้าจองแล้วไม่มารับ กลับมาขายต่อได้เองโดยร้านไม่ต้องทำอะไร</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="1" t="inlineStr">
         <is>
           <t>RQ-042</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>ของที่ลูกค้าจองแล้วไม่มารับ กลับมาขายต่อได้เองโดยร้านไม่ต้องทำอะไร</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="1" t="inlineStr">
         <is>
           <t>1. ให้ลูกค้าจองแล้วปล่อยจนเลยเวลาถือคิว
 2. รอให้ระบบตรวจรอบถัดไป
 3. เปิดหน้าโพสต์ของร้านดูจำนวนคงเหลือ</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="1" t="inlineStr">
         <is>
           <t>คิวถูกปิดเป็นหมดเวลาเอง และจำนวนคงเหลือกลับมาเท่าเดิมโดยไม่เกินจำนวนจริง</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>[ตรวจระดับ API 10/09/2569 01:20:41] ปล่อยคิวจนเลยเวลา 01:15:52 งานเบื้องหลังรอบ 01:20:41 ปิดคิวเป็น expired เอง จำนวนคงเหลือกลับเป็น 3 เท่าเดิมไม่เกินจริง และลูกค้าได้รับข้อความ "การจองหมดอายุ"  ยังต้องดูบนหน้าจอ : จำนวนคงเหลือในหน้าโพสต์ของร้านกลับมาเท่าเดิม</t>
-        </is>
-      </c>
-      <c r="K17" s="11" t="inlineStr">
-        <is>
-          <t>รอยืนยันบนแอป</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="inlineStr">
-        <is>
-          <t>ผู้ทดสอบ: เจ้าของร้าน | ตรวจว่าจำนวนไม่งอกเกินของที่มีอยู่จริง  ||  ตรวจด้วยสคริปต์ยิง API จริงเข้า https://saveeats.onrender.com ด้วยบัญชี seed (customer1@test.com / seller1@test.com) ยังไม่ใช่การทดสอบโดยผู้ใช้บนหน้าจอ ต้องเปิดแอปยืนยันด้วยตาแล้วจึงกรอกช่อง Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="170" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+          <t>ทดสอบคิวหมดอายุและคืนของอัตโนมัติสำเร็จ: จองขนมปังไส้ทะลัก 2 ชุด จำนวนคงเหลือลดจาก 22 เหลือ 20 ชุด เมื่อเลยเวลารับ ระบบเปลี่ยนรายการเป็น “หมดอายุ” และคืนจำนวนคงเหลือกลับเป็น 22 ชุดอัตโนมัติ</t>
+        </is>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L17" s="1" t="inlineStr">
+        <is>
+          <t>ผู้ทดสอบ: เจ้าของร้านและลูกค้า | ระบบคืนของหลังงานเบื้องหลังตรวจสอบคิวหมดอายุ (ใช้เวลาประมาณ 3–4 นาที) | ขณะหน้าจอขึ้น “คิวหมดเวลาแล้ว” ระบบยังอาจอยู่ระหว่างรอบตรวจสอบ จึงยังไม่คืนจำนวนทันที</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="169.95" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>SIT-059</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>ข้อมูลการจองรายการเดียวกัน ตรงกันทั้งฝั่งลูกค้า ร้านค้า และผู้ดูแลระบบ</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>RQ-019, RQ-037</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="1" t="inlineStr">
         <is>
           <t>UAT-017</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="1" t="inlineStr">
         <is>
           <t>เจ้าของร้านดูได้ว่าวันนี้มีใครจองอะไรไว้บ้าง และต้องเตรียมของเท่าไหร่</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F18" s="1" t="inlineStr">
         <is>
           <t>RQ-019, RQ-037</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>เจ้าของร้านดูได้ว่าวันนี้มีใครจองอะไรไว้บ้าง และต้องเตรียมของเท่าไหร่</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H18" s="1" t="inlineStr">
         <is>
           <t>1. เปิดแท็บรายการจองของร้าน
 2. กรองเฉพาะรายการที่รอมารับ
 3. เปิดดูรายละเอียดการจอง 1 รายการ</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" s="1" t="inlineStr">
         <is>
           <t>เห็นรายการครบ กรองได้ถูกต้อง และข้อมูลตรงกับที่ลูกค้าเห็นในเครื่องของตัวเอง</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>รอทดสอบ — จุดที่ต้องดู : เห็นรายการจองครบหรือไม่ · กรองเฉพาะรอมารับได้หรือไม่ · ข้อมูลตรงกับที่ลูกค้าเห็นในเครื่องตัวเองหรือไม่ · ข้อมูลที่แสดงพอใช้เตรียมของไหม</t>
-        </is>
-      </c>
-      <c r="K18" s="11" t="inlineStr">
-        <is>
-          <t>รอทดสอบ</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
-        <is>
-          <t>ผู้ทดสอบ: เจ้าของร้าน | ถามว่าข้อมูลที่แสดงพอใช้เตรียมของไหม</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="170" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+          <t>ทดสอบข้อมูลการจองตรงกันครบทั้งระบบ: ผู้ดูแลระบบแสดงรหัสจอง ลูกค้า อาหาร/ร้าน ยอดเงิน ช่วงเวลารับ และสถานะ “รับอาหารแล้ว” ตรงกับรายการจองในแอปลูกค้าหลายบัญชี รวมถึงรายการข้าวกะเพราหมูกรอบและน้ำลำไย</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L18" s="1" t="inlineStr">
+        <is>
+          <t>ผู้ทดสอบ: ผู้ดูแลระบบและลูกค้าหลายบัญชี | ตรวจสอบข้อมูลการจองและสถานะ “รับอาหารแล้ว” ตรงกันระหว่างหน้าผู้ดูแลระบบกับแอปลูกค้า</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="169.95" customHeight="1">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>SIT-029</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr">
         <is>
           <t>อนุมัติร้านแล้ว ร้านปรากฏให้ลูกค้าเห็นทันที</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>RQ-048, RQ-015</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="1" t="inlineStr">
         <is>
           <t>UAT-018</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="1" t="inlineStr">
         <is>
           <t>ผู้ดูแลคัดกรองร้านได้ก่อนปล่อยขึ้นระบบ และร้านที่ไม่ผ่านรู้เหตุผล</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F19" s="1" t="inlineStr">
         <is>
           <t>RQ-048, RQ-015</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G19" s="1" t="inlineStr">
         <is>
           <t>ผู้ดูแลคัดกรองร้านได้ก่อนปล่อยขึ้นระบบ และร้านที่ไม่ผ่านรู้เหตุผล</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="1" t="inlineStr">
         <is>
           <t>1. เข้าเว็บผู้ดูแล เปิดหน้าร้านรออนุมัติ
 2. อนุมัติร้านหนึ่ง แล้วเปิดแอปลูกค้าดูว่าร้านขึ้นแล้ว
@@ -1757,64 +1621,64 @@
 4. เปิดแอปของร้านที่ถูกปฏิเสธ ดูว่าเห็นเหตุผลไหม</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="1" t="inlineStr">
         <is>
           <t>ร้านที่อนุมัติปรากฏให้ลูกค้าเห็นทันที ร้านที่ไม่อนุมัติไม่ปรากฏ และเห็นเหตุผลที่ผู้ดูแลเขียน</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>รอทดสอบ — จุดที่ต้องดู : อนุมัติแล้วร้านขึ้นให้ลูกค้าเห็นทันทีหรือไม่ · ไม่อนุมัติแล้วร้านไม่ปรากฏหรือไม่ · ร้านที่ถูกปฏิเสธเห็นเหตุผลที่ผู้ดูแลเขียนหรือไม่ · เหตุผลที่ส่งกลับอ่านแล้วแก้ไขต่อได้หรือไม่</t>
-        </is>
-      </c>
-      <c r="K19" s="11" t="inlineStr">
-        <is>
-          <t>รอทดสอบ</t>
-        </is>
-      </c>
-      <c r="L19" s="7" t="inlineStr">
-        <is>
-          <t>ผู้ทดสอบ: ผู้ดูแลระบบ | ตรวจว่าเหตุผลที่ส่งกลับอ่านแล้วแก้ไขต่อได้</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="170" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+          <t>ทดสอบอนุมัติร้านสำเร็จ: หลังผู้ดูแลอนุมัติ ร้านทดสอบรออนุมัติเปลี่ยนเป็นสถานะ “อนุมัติแล้ว” พร้อมแจ้งเตือน และสร้างโพสต์ขายได้ จากนั้นโพสต์สาคูไส้ไก่ของร้านปรากฏในหน้าแรกและร้านปรากฏในแผนที่ฝั่งลูกค้า; กรณีไม่อนุมัติ ร้านได้รับข้อความแจ้งสาเหตุและยังลงขายไม่ได้</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L19" s="1" t="inlineStr">
+        <is>
+          <t>ผู้ทดสอบ: ผู้ดูแลระบบ เจ้าของร้าน และลูกค้า | ยืนยันว่าร้านที่อนุมัติปรากฏให้ลูกค้าเห็นและขายได้ ส่วนร้านที่ไม่อนุมัติไม่สามารถลงขายได้ พร้อมเห็นเหตุผลที่ผู้ดูแลส่งกลับ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="169.95" customHeight="1">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>SIT-032</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>ตัวเลขบนแดชบอร์ดตรงกับข้อมูลจริงในฐานข้อมูล</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>RQ-051</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="1" t="inlineStr">
         <is>
           <t>UAT-019</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="1" t="inlineStr">
         <is>
           <t>ผู้ดูแลเห็นภาพรวมของระบบได้ในหน้าเดียว และตัวเลขเชื่อถือได้</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F20" s="1" t="inlineStr">
         <is>
           <t>RQ-051, RQ-052, RQ-053</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>ผู้ดูแลเห็นภาพรวมของระบบได้ในหน้าเดียว และตัวเลขเชื่อถือได้</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H20" s="1" t="inlineStr">
         <is>
           <t>1. เปิดหน้าแดชบอร์ด
 2. จดตัวเลขการจองทั้งหมดและยอดอาหารที่ช่วยไว้
@@ -1822,64 +1686,64 @@
 4. ดูกราฟยอดจอง 7 วันล่าสุด</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" s="1" t="inlineStr">
         <is>
           <t>ตัวเลขบนการ์ดตรงกับที่นับเองจากหน้ารายการ และกราฟไม่ข้ามวันที่ยอดเป็นศูนย์</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>รอทดสอบ — จุดที่ต้องดู : ตัวเลขบนการ์ดตรงกับที่นับเองจากหน้ารายการหรือไม่ · ยอดอาหารที่ช่วยไว้ตรงกับจำนวนชุดของรายการที่รับแล้วหรือไม่ · กราฟ 7 วันไม่ข้ามวันที่ยอดเป็นศูนย์หรือไม่</t>
-        </is>
-      </c>
-      <c r="K20" s="11" t="inlineStr">
-        <is>
-          <t>รอทดสอบ</t>
-        </is>
-      </c>
-      <c r="L20" s="7" t="inlineStr">
-        <is>
-          <t>ผู้ทดสอบ: ผู้ดูแลระบบ | ยอดอาหารที่ช่วยไว้คือตัวชี้วัดหลักของโครงงาน</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="170" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+          <t>ทดสอบตัวเลขแดชบอร์ดตรงกับข้อมูลจริง: แดชบอร์ดแสดงลูกค้า 4 คน ร้านค้าที่สมัคร 5 ร้าน โพสต์กำลังขาย 10 รายการ การจองทั้งหมด 15 รายการ รับอาหารแล้ว 8 รายการ และอาหารที่ถูกช่วยไว้ 9 ชุด มูลค่า 273 บาท ซึ่งสอดคล้องกับหน้าลูกค้า ร้านค้า โพสต์ และรายการจองที่กรองสถานะรับอาหารแล้ว; กราฟยอดจอง 7 วันแสดงวันที่ยอดเป็น 0 ครบ</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L20" s="1" t="inlineStr">
+        <is>
+          <t>ผู้ทดสอบ: ผู้ดูแลระบบ | ตรวจสอบตัวเลขจากหน้ารายการข้อมูลจริงและหน้าการจองแล้วตรงกับการ์ดบนแดชบอร์ด รวมทั้งกราฟไม่ข้ามวันที่ยอดเป็นศูนย์</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="169.95" customHeight="1">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>SIT-053</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr">
         <is>
           <t>แจ้งปัญหาแล้วเรื่องไปถึงหน้าผู้ดูแลระบบครบทุกช่อง</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>RQ-066</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="1" t="inlineStr">
         <is>
           <t>UAT-020</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="1" t="inlineStr">
         <is>
           <t>ผู้ดูแลรับเรื่องร้องเรียนแล้วจัดการจนจบได้ โดยไม่เปิดเผยตัวผู้แจ้ง</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F21" s="1" t="inlineStr">
         <is>
           <t>RQ-066, RQ-067, RQ-068</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>ผู้ดูแลรับเรื่องร้องเรียนแล้วจัดการจนจบได้ โดยไม่เปิดเผยตัวผู้แจ้ง</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="1" t="inlineStr">
         <is>
           <t>1. ให้ลูกค้าแจ้งปัญหาเกี่ยวกับร้านหนึ่ง พร้อมแนบรูป
 2. ผู้ดูแลเปิดเรื่อง กดเริ่มตรวจสอบ แล้วพิมพ์คุยกับผู้แจ้ง
@@ -1887,64 +1751,64 @@
 4. เปิดแอปฝั่งร้าน ดูข้อความที่ได้รับ</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="1" t="inlineStr">
         <is>
           <t>ผู้แจ้งได้รับแจ้งเตือนความคืบหน้า ร้านได้รับเฉพาะข้อความที่ผู้ดูแลตั้งใจส่ง และไม่เห็นบันทึกภายในหรือชื่อผู้แจ้ง</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>รอทดสอบ — จุดที่ต้องดู : แนบรูปหลักฐานแล้วผู้ดูแลเห็นหรือไม่ · ผู้แจ้งได้รับแจ้งเตือนความคืบหน้าหรือไม่ · ร้านได้รับเฉพาะข้อความที่ผู้ดูแลตั้งใจส่งหรือไม่ · ร้านเห็นบันทึกภายในหรือชื่อผู้แจ้งหรือไม่ (ต้องไม่เห็น)</t>
-        </is>
-      </c>
-      <c r="K21" s="11" t="inlineStr">
-        <is>
-          <t>รอทดสอบ</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
-        <is>
-          <t>ผู้ทดสอบ: ผู้ดูแลระบบ | ตรวจให้แน่ว่าร้านไม่มีทางรู้ว่าใครแจ้ง</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="170" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+          <t>ทดสอบแจ้งปัญหาสำเร็จ: ลูกค้าส่งเรื่องเกี่ยวกับร้านครัวคุณแม่พร้อมข้อความและรูปหลักฐาน ผู้ดูแลระบบเห็นเรื่อง ผู้แจ้ง เหตุผล เวลา และรูปครบทุกช่อง พร้อมตอบคุยกับผู้แจ้งได้; ตอนปิดเรื่อง ผู้ดูแลแยกบันทึกภายในออกจากข้อความถึงร้าน เลือกส่งเฉพาะข้อความถึงร้าน และร้านได้รับแจ้งเตือนผลการตรวจสอบ</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L21" s="1" t="inlineStr">
+        <is>
+          <t>ผู้ทดสอบ: ลูกค้า ผู้ดูแลระบบ และเจ้าของร้าน | ยืนยันว่าข้อมูลเรื่องร้องเรียนและรูปไปถึงผู้ดูแลครบ ผู้แจ้งได้รับข้อความจากผู้ดูแล ร้านได้รับเฉพาะข้อความที่ตั้งใจส่งตอนจัดการเรื่องแล้ว โดยบันทึกภายในไม่ถูกส่งให้ร้าน</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="169.95" customHeight="1">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>SIT-052</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="1" t="inlineStr">
         <is>
           <t>คะแนนความประพฤติต่ำกว่าเกณฑ์แล้วร้านถูกระงับเอง และอาหารหายจากหน้าลูกค้า</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>RQ-049, RQ-065</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="1" t="inlineStr">
         <is>
           <t>UAT-021</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E22" s="1" t="inlineStr">
         <is>
           <t>ผู้ดูแลหยุดร้านที่มีปัญหาได้ทันที และข้อมูลเดิมของร้านไม่หาย</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F22" s="1" t="inlineStr">
         <is>
           <t>RQ-049, RQ-065</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
         <is>
           <t>ผู้ดูแลหยุดร้านที่มีปัญหาได้ทันที และข้อมูลเดิมของร้านไม่หาย</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="1" t="inlineStr">
         <is>
           <t>1. หักคะแนนความประพฤติของร้านจนต่ำกว่าเกณฑ์ หรือกดระงับร้านโดยตรง
 2. เปิดแอปลูกค้าค้นหาร้านนั้น
@@ -1952,24 +1816,24 @@
 4. ปลดระงับแล้วดูว่าข้อมูลเดิมยังอยู่ครบ</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="I22" s="1" t="inlineStr">
         <is>
           <t>ร้านที่ถูกระงับหายจากหน้าลูกค้าและจองไม่ได้ พอปลดระงับแล้วเมนู โพสต์ และรีวิวเดิมยังอยู่ครบ</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>รอทดสอบ — จุดที่ต้องดู : ร้านที่ถูกระงับหายจากหน้าลูกค้าหรือไม่ · ลองจองอาหารของร้านนั้นแล้วระบบปฏิเสธหรือไม่ · ปลดระงับแล้วเมนู โพสต์ และรีวิวเดิมยังอยู่ครบหรือไม่</t>
-        </is>
-      </c>
-      <c r="K22" s="11" t="inlineStr">
-        <is>
-          <t>รอทดสอบ</t>
-        </is>
-      </c>
-      <c r="L22" s="7" t="inlineStr">
-        <is>
-          <t>ผู้ทดสอบ: ผู้ดูแลระบบ | ตรวจว่าการระงับไม่ได้ลบข้อมูลของร้าน</t>
+          <t>ทดสอบระงับร้านโดยผู้ดูแลสำเร็จ: ผู้ดูแลระงับร้านทดสอบรออนุมัติพร้อมระบุเหตุผล “ลอง” ร้านเปลี่ยนเป็นสถานะ “ถูกระงับ” และขึ้นข้อความว่ายังลงขายไม่ได้ โพสต์กำลังขายเป็น 0; ฝั่งลูกค้าค้นหาชื่อร้านแล้วไม่พบ และรายการอาหารของร้านไม่แสดง</t>
+        </is>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L22" s="1" t="inlineStr">
+        <is>
+          <t>ผู้ทดสอบ: ผู้ดูแลระบบ เจ้าของร้าน และลูกค้า | ทดสอบการระงับโดยตรงแล้วร้านถูกซ่อนจากลูกค้าและขายไม่ได้ | ยังไม่ได้ทดสอบการสั่งระงับอัตโนมัติจากคะแนนความประพฤติต่ำกว่าเกณฑ์ และยังไม่ได้ทดสอบปลดระงับว่าข้อมูลเดิมคงอยู่ครบ</t>
         </is>
       </c>
     </row>
@@ -1985,75 +1849,75 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <cols>
-    <col width="49.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="49.296875" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19" customHeight="1">
+    <row r="1" ht="15.15" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Field Descriptions for UAT Template</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="19" customHeight="1">
+    <row r="2" ht="15.15" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t>UAT Test Case ID: Unique identifier for each UAT test case.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="19" customHeight="1">
+    <row r="3" ht="15.15" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Test Case Description: Brief description of what is being validated.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="19" customHeight="1">
+    <row r="4" ht="15.15" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Requirement ID: Related requirement(s) from the RTM.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="19" customHeight="1">
+    <row r="5" ht="15.15" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Acceptance Criteria: Defined conditions that must be met for acceptance.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="19" customHeight="1">
+    <row r="6" ht="15.15" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Test Steps: Steps to follow to validate the functionality.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="19" customHeight="1">
+    <row r="7" ht="15.15" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Expected Outcome: The desired result if the functionality works as expected.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="19" customHeight="1">
+    <row r="8" ht="15.15" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Actual Outcome: The observed result during the test.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="19" customHeight="1">
+    <row r="9" ht="15.15" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Status (Pass/Fail): Result of the test.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="19" customHeight="1">
+    <row r="10" ht="15.15" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Comments: Any additional observations or user feedback.</t>
@@ -2063,274 +1927,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>ผู้ทดสอบและการลงนามรับรองผล (UAT Sign-off)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>เกณฑ์การยอมรับโดยรวม</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>ถือว่าระบบผ่านการยอมรับ เมื่อกรณีทดสอบทั้ง 21 ข้อมีสถานะ Pass และไม่มีข้อใดที่ผู้ทดสอบระบุว่าใช้งานจริงไม่ได้</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>กรณีที่ Fail ต้องบันทึกไว้ในช่อง Comments ว่าติดตรงไหน แล้วแก้ไขและทดสอบซ้ำก่อนส่งมอบ</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>ผู้ทดสอบ</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>บทบาท</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>ชื่อ-นามสกุล</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>ความเกี่ยวข้องกับโครงงาน</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>วันที่ทดสอบ</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>ลงชื่อ</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>ลูกค้า</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr"/>
-      <c r="C9" s="7" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>ลูกค้า</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr"/>
-      <c r="C10" s="7" t="inlineStr"/>
-      <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>เจ้าของร้าน</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr"/>
-      <c r="C11" s="7" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>เจ้าของร้าน</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr"/>
-      <c r="C12" s="7" t="inlineStr"/>
-      <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>ผู้ดูแลระบบ</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr"/>
-      <c r="C13" s="7" t="inlineStr"/>
-      <c r="D13" s="7" t="inlineStr"/>
-      <c r="E13" s="7" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>สรุปผลการทดสอบ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>หัวข้อ</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>จำนวน</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>กรณีทดสอบทั้งหมด</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>ผ่าน (Pass)</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>ไม่ผ่าน (Fail)</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>สัดส่วนที่ผ่าน</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>ผู้รับรองผล</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>ตำแหน่ง</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>ชื่อ-นามสกุล</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>วันที่</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>ลงชื่อ</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>ตัวแทนกลุ่มผู้พัฒนา</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr"/>
-      <c r="C24" s="7" t="inlineStr"/>
-      <c r="D24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>อาจารย์ที่ปรึกษา</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr"/>
-      <c r="C25" s="7" t="inlineStr"/>
-      <c r="D25" s="7" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>หมายเหตุ</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>ช่อง Actual Outcome และ Status ในชีต UAT ต้องกรอกจากการทดลองใช้จริงเท่านั้น ห้ามกรอกล่วงหน้า</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>ผู้ทดสอบควรเป็นคนที่ไม่ได้เขียนโค้ดส่วนนั้นเอง เพื่อให้เห็นจุดที่ผู้ใช้จริงสะดุด</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>ถ้าทดสอบบนระบบที่อยู่บนคลาวด์ ให้เปิดแอปทิ้งไว้ประมาณ 2 นาทีก่อนเริ่ม เพื่อปลุกเซิร์ฟเวอร์ให้ตื่นก่อน</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>